--- a/Outputs/Recycling_Plot_Data/Repeal/01_Geofacet_StateMass_2050_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/01_Geofacet_StateMass_2050_data_Repeal.xlsx
@@ -775,7 +775,7 @@
         <v>2050</v>
       </c>
       <c r="F15">
-        <v>0.2550112070122972</v>
+        <v>0.2547952255606796</v>
       </c>
     </row>
     <row r="16">
@@ -1111,7 +1111,7 @@
         <v>2050</v>
       </c>
       <c r="F27">
-        <v>0.1551318175991474</v>
+        <v>0.1550004288827467</v>
       </c>
     </row>
     <row r="28">
@@ -1139,7 +1139,7 @@
         <v>2050</v>
       </c>
       <c r="F28">
-        <v>0.353084001421579</v>
+        <v>0.3527849573283274</v>
       </c>
     </row>
     <row r="29">
@@ -1419,7 +1419,7 @@
         <v>2050</v>
       </c>
       <c r="F38">
-        <v>1.199114103387622</v>
+        <v>1.190265225702146</v>
       </c>
     </row>
     <row r="39">
@@ -1447,7 +1447,7 @@
         <v>2050</v>
       </c>
       <c r="F39">
-        <v>0.8749824049938242</v>
+        <v>0.8742413396415029</v>
       </c>
     </row>
     <row r="40">
@@ -1475,7 +1475,7 @@
         <v>2050</v>
       </c>
       <c r="F40">
-        <v>0.03007408468248713</v>
+        <v>0.03004861347068473</v>
       </c>
     </row>
     <row r="41">
@@ -1503,7 +1503,7 @@
         <v>2050</v>
       </c>
       <c r="F41">
-        <v>0.6553401661159952</v>
+        <v>0.6476816811723666</v>
       </c>
     </row>
     <row r="42">
@@ -1643,7 +1643,7 @@
         <v>2050</v>
       </c>
       <c r="F46">
-        <v>0.004645842123968145</v>
+        <v>0.004641907333267466</v>
       </c>
     </row>
     <row r="47">
@@ -2315,7 +2315,7 @@
         <v>2050</v>
       </c>
       <c r="F70">
-        <v>0.009291684247936291</v>
+        <v>0.009283814666534933</v>
       </c>
     </row>
     <row r="71">
@@ -2455,7 +2455,7 @@
         <v>2050</v>
       </c>
       <c r="F75">
-        <v>0.9778366094824867</v>
+        <v>0.9770084318787051</v>
       </c>
     </row>
     <row r="76">
@@ -2483,7 +2483,7 @@
         <v>2050</v>
       </c>
       <c r="F76">
-        <v>0.8486404946448479</v>
+        <v>0.8479217395435237</v>
       </c>
     </row>
     <row r="77">
@@ -3127,7 +3127,7 @@
         <v>2050</v>
       </c>
       <c r="F99">
-        <v>0.07727612333705976</v>
+        <v>0.07721067441232715</v>
       </c>
     </row>
     <row r="100">
@@ -3155,7 +3155,7 @@
         <v>2050</v>
       </c>
       <c r="F100">
-        <v>0.5575010548761776</v>
+        <v>0.5570288799920959</v>
       </c>
     </row>
     <row r="101">
@@ -3295,7 +3295,7 @@
         <v>2050</v>
       </c>
       <c r="F105">
-        <v>0.2894763580206259</v>
+        <v>0.2892311863485775</v>
       </c>
     </row>
     <row r="106">
@@ -3323,7 +3323,7 @@
         <v>2050</v>
       </c>
       <c r="F106">
-        <v>0.6445951085601669</v>
+        <v>0.6440491694664165</v>
       </c>
     </row>
     <row r="107">
@@ -3491,7 +3491,7 @@
         <v>2050</v>
       </c>
       <c r="F112">
-        <v>0.1858336849587258</v>
+        <v>0.1856762933306987</v>
       </c>
     </row>
     <row r="113">
@@ -3631,7 +3631,7 @@
         <v>2050</v>
       </c>
       <c r="F117">
-        <v>0.4404739030212406</v>
+        <v>0.4401008441502647</v>
       </c>
     </row>
     <row r="118">
@@ -3659,7 +3659,7 @@
         <v>2050</v>
       </c>
       <c r="F118">
-        <v>0.1610558602975624</v>
+        <v>0.1609194542199388</v>
       </c>
     </row>
     <row r="119">
@@ -3967,7 +3967,7 @@
         <v>2050</v>
       </c>
       <c r="F129">
-        <v>0.08502691850776685</v>
+        <v>0.08495490505588355</v>
       </c>
     </row>
     <row r="130">
@@ -4331,7 +4331,7 @@
         <v>2050</v>
       </c>
       <c r="F142">
-        <v>0.001238891233058172</v>
+        <v>0.001237841955537991</v>
       </c>
     </row>
     <row r="143">
@@ -4639,7 +4639,7 @@
         <v>2050</v>
       </c>
       <c r="F153">
-        <v>1.570266281433722</v>
+        <v>1.56893634619337</v>
       </c>
     </row>
     <row r="154">
@@ -4667,7 +4667,7 @@
         <v>2050</v>
       </c>
       <c r="F154">
-        <v>1.000590504379433</v>
+        <v>0.9997430553902582</v>
       </c>
     </row>
     <row r="155">
@@ -5003,7 +5003,7 @@
         <v>2050</v>
       </c>
       <c r="F166">
-        <v>0.001238891233058172</v>
+        <v>0.001237841955537991</v>
       </c>
     </row>
     <row r="167">
@@ -5171,7 +5171,7 @@
         <v>2050</v>
       </c>
       <c r="F172">
-        <v>0.1300835794711081</v>
+        <v>0.1299734053314891</v>
       </c>
     </row>
     <row r="173">
@@ -5479,7 +5479,7 @@
         <v>2050</v>
       </c>
       <c r="F183">
-        <v>0.0676166079199273</v>
+        <v>0.06755934011078625</v>
       </c>
     </row>
     <row r="184">
@@ -5535,7 +5535,7 @@
         <v>2050</v>
       </c>
       <c r="F185">
-        <v>0.5477544793648994</v>
+        <v>0.5476838187546399</v>
       </c>
     </row>
     <row r="186">
@@ -5815,7 +5815,7 @@
         <v>2050</v>
       </c>
       <c r="F195">
-        <v>0.5305778628322523</v>
+        <v>0.5301284905150382</v>
       </c>
     </row>
     <row r="196">
@@ -5843,7 +5843,7 @@
         <v>2050</v>
       </c>
       <c r="F196">
-        <v>0.1920281411240167</v>
+        <v>0.1918655031083886</v>
       </c>
     </row>
     <row r="197">
@@ -6319,7 +6319,7 @@
         <v>2050</v>
       </c>
       <c r="F213">
-        <v>7.727612333705977E-05</v>
+        <v>7.721067441232715E-05</v>
       </c>
     </row>
     <row r="214">
@@ -7495,7 +7495,7 @@
         <v>2050</v>
       </c>
       <c r="F255">
-        <v>1.275056035061486</v>
+        <v>1.273976127803398</v>
       </c>
     </row>
     <row r="256">
@@ -7523,7 +7523,7 @@
         <v>2050</v>
       </c>
       <c r="F256">
-        <v>0.06411262131076041</v>
+        <v>0.06405832119909102</v>
       </c>
     </row>
     <row r="257">
@@ -7663,7 +7663,7 @@
         <v>2050</v>
       </c>
       <c r="F261">
-        <v>0.2511474008454442</v>
+        <v>0.2509346918400632</v>
       </c>
     </row>
     <row r="262">
@@ -7691,7 +7691,7 @@
         <v>2050</v>
       </c>
       <c r="F262">
-        <v>0.003406950890909974</v>
+        <v>0.003404065377729476</v>
       </c>
     </row>
     <row r="263">
@@ -7831,7 +7831,7 @@
         <v>2050</v>
       </c>
       <c r="F267">
-        <v>0.7127176855377023</v>
+        <v>0.7121140501048934</v>
       </c>
     </row>
     <row r="268">
@@ -7859,7 +7859,7 @@
         <v>2050</v>
       </c>
       <c r="F268">
-        <v>0.5079454055538506</v>
+        <v>0.5075152017705763</v>
       </c>
     </row>
     <row r="269">
@@ -8167,7 +8167,7 @@
         <v>2050</v>
       </c>
       <c r="F279">
-        <v>0.5458864610092298</v>
+        <v>0.5454241230922084</v>
       </c>
     </row>
     <row r="280">
@@ -8195,7 +8195,7 @@
         <v>2050</v>
       </c>
       <c r="F280">
-        <v>1.093321513173837</v>
+        <v>1.092395525762277</v>
       </c>
     </row>
     <row r="281">
@@ -8531,7 +8531,7 @@
         <v>2050</v>
       </c>
       <c r="F292">
-        <v>0.0004336119315703603</v>
+        <v>0.0004332446844382968</v>
       </c>
     </row>
     <row r="293">
@@ -8839,7 +8839,7 @@
         <v>2050</v>
       </c>
       <c r="F303">
-        <v>0.03863806166852988</v>
+        <v>0.03860533720616358</v>
       </c>
     </row>
     <row r="304">
@@ -8867,7 +8867,7 @@
         <v>2050</v>
       </c>
       <c r="F304">
-        <v>0.001238891233058172</v>
+        <v>0.001237841955537991</v>
       </c>
     </row>
     <row r="305">
@@ -9175,7 +9175,7 @@
         <v>2050</v>
       </c>
       <c r="F315">
-        <v>0.04605656950888762</v>
+        <v>0.04601756194974697</v>
       </c>
     </row>
     <row r="316">
@@ -9203,7 +9203,7 @@
         <v>2050</v>
       </c>
       <c r="F316">
-        <v>0.04336119315703602</v>
+        <v>0.04332446844382967</v>
       </c>
     </row>
     <row r="317">
@@ -9679,7 +9679,7 @@
         <v>2050</v>
       </c>
       <c r="F333">
-        <v>1.407970967201229</v>
+        <v>1.4067784877926</v>
       </c>
     </row>
     <row r="334">
@@ -9707,7 +9707,7 @@
         <v>2050</v>
       </c>
       <c r="F334">
-        <v>0.5946677918679226</v>
+        <v>0.5941641386582357</v>
       </c>
     </row>
     <row r="335">
@@ -9847,7 +9847,7 @@
         <v>2050</v>
       </c>
       <c r="F339">
-        <v>0.8113992950391276</v>
+        <v>0.8107120813294351</v>
       </c>
     </row>
     <row r="340">
@@ -9875,7 +9875,7 @@
         <v>2050</v>
       </c>
       <c r="F340">
-        <v>0.06194456165290861</v>
+        <v>0.06189209777689954</v>
       </c>
     </row>
     <row r="341">
@@ -10183,7 +10183,7 @@
         <v>2050</v>
       </c>
       <c r="F351">
-        <v>0.01545522466741195</v>
+        <v>0.01544213488246543</v>
       </c>
     </row>
     <row r="352">
@@ -10883,7 +10883,7 @@
         <v>2050</v>
       </c>
       <c r="F376">
-        <v>0.09291684247936292</v>
+        <v>0.09283814666534933</v>
       </c>
     </row>
     <row r="377">
